--- a/CPRI.xlsx
+++ b/CPRI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D820024-CDDD-4AFA-8FD6-CB2A80445868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5740421C-C320-43E2-9E22-9F4EFAFCB704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{973D8E1F-BCD0-4D20-A01B-2C85341BD8AE}"/>
   </bookViews>
@@ -39,10 +39,37 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={A0717645-D1AF-468B-8510-1BAD8A122BB4}</author>
+    <author>tc={84920B80-BB2D-4412-BFFE-F1946822EADE}</author>
+    <author>tc={4CCC7B31-B206-4428-9371-211109658E48}</author>
+    <author>tc={47D399BF-1926-4A67-A37C-C53AB4BB2BE7}</author>
+    <author>tc={97B87964-98A8-446C-8CE5-CF6961AAB303}</author>
   </authors>
   <commentList>
-    <comment ref="K40" authorId="0" shapeId="0" xr:uid="{A0717645-D1AF-468B-8510-1BAD8A122BB4}">
+    <comment ref="K40" authorId="0" shapeId="0" xr:uid="{84920B80-BB2D-4412-BFFE-F1946822EADE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only -6% excluding the devestiture of Versace</t>
+      </text>
+    </comment>
+    <comment ref="L40" authorId="1" shapeId="0" xr:uid="{4CCC7B31-B206-4428-9371-211109658E48}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only -6% excluding the devestiture of Versace</t>
+      </text>
+    </comment>
+    <comment ref="M40" authorId="2" shapeId="0" xr:uid="{47D399BF-1926-4A67-A37C-C53AB4BB2BE7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only -6% excluding the devestiture of Versace</t>
+      </text>
+    </comment>
+    <comment ref="N40" authorId="3" shapeId="0" xr:uid="{97B87964-98A8-446C-8CE5-CF6961AAB303}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -174,9 +201,6 @@
     <t>Net Income</t>
   </si>
   <si>
-    <t>Minority Interest Share</t>
-  </si>
-  <si>
     <t>Net Income to Company</t>
   </si>
   <si>
@@ -287,6 +311,9 @@
   <si>
     <t>Q426</t>
   </si>
+  <si>
+    <t>Dis. Op &amp; Minority Interest</t>
+  </si>
 </sst>
 </file>
 
@@ -296,13 +323,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -503,43 +536,44 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -882,7 +916,16 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="K40" dT="2025-09-28T14:32:09.82" personId="{AFB1407E-778A-419C-957C-A69B47F6A8E2}" id="{A0717645-D1AF-468B-8510-1BAD8A122BB4}">
+  <threadedComment ref="K40" dT="2025-09-28T14:32:09.82" personId="{AFB1407E-778A-419C-957C-A69B47F6A8E2}" id="{84920B80-BB2D-4412-BFFE-F1946822EADE}">
+    <text>Only -6% excluding the devestiture of Versace</text>
+  </threadedComment>
+  <threadedComment ref="L40" dT="2025-09-28T14:32:09.82" personId="{AFB1407E-778A-419C-957C-A69B47F6A8E2}" id="{4CCC7B31-B206-4428-9371-211109658E48}">
+    <text>Only -6% excluding the devestiture of Versace</text>
+  </threadedComment>
+  <threadedComment ref="M40" dT="2025-09-28T14:32:09.82" personId="{AFB1407E-778A-419C-957C-A69B47F6A8E2}" id="{47D399BF-1926-4A67-A37C-C53AB4BB2BE7}">
+    <text>Only -6% excluding the devestiture of Versace</text>
+  </threadedComment>
+  <threadedComment ref="N40" dT="2025-09-28T14:32:09.82" personId="{AFB1407E-778A-419C-957C-A69B47F6A8E2}" id="{97B87964-98A8-446C-8CE5-CF6961AAB303}">
     <text>Only -6% excluding the devestiture of Versace</text>
   </threadedComment>
 </ThreadedComments>
@@ -914,7 +957,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>19.670000000000002</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -922,10 +965,10 @@
         <v>3</v>
       </c>
       <c r="I3" s="3">
-        <v>119.048057</v>
+        <v>118.798219</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -937,7 +980,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I3*I2</f>
-        <v>2341.6752811900001</v>
+        <v>2154.9996926600002</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -948,10 +991,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="3">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -959,11 +1002,11 @@
         <v>6</v>
       </c>
       <c r="I6" s="3">
-        <f>1650+21</f>
-        <v>1671</v>
+        <f>14+343</f>
+        <v>357</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -975,7 +1018,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>3883.6752811900001</v>
+        <v>2376.9996926600002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1023,7 +1066,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1075,39 +1118,39 @@
         <v>27</v>
       </c>
       <c r="K2" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="M2" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="M2" s="24" t="s">
+      <c r="N2" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="N2" s="24" t="s">
-        <v>76</v>
-      </c>
       <c r="P2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3" s="18">
         <v>224</v>
@@ -1137,8 +1180,12 @@
         <v>0</v>
       </c>
       <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
+      <c r="M3" s="18">
+        <v>0</v>
+      </c>
+      <c r="N3" s="18">
+        <v>0</v>
+      </c>
       <c r="O3" s="3"/>
       <c r="P3" s="18"/>
       <c r="Q3" s="18"/>
@@ -1167,7 +1214,7 @@
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="18">
         <v>237</v>
@@ -1197,9 +1244,15 @@
         <f>161+56</f>
         <v>217</v>
       </c>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="L4" s="18">
+        <v>216</v>
+      </c>
+      <c r="M4" s="18">
+        <v>214</v>
+      </c>
+      <c r="N4" s="18">
+        <v>211</v>
+      </c>
       <c r="O4" s="3"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="18"/>
@@ -1228,7 +1281,7 @@
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="18">
         <v>810</v>
@@ -1258,9 +1311,15 @@
         <f>384+311</f>
         <v>695</v>
       </c>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
+      <c r="L5" s="18">
+        <v>691</v>
+      </c>
+      <c r="M5" s="18">
+        <v>694</v>
+      </c>
+      <c r="N5" s="18">
+        <v>673</v>
+      </c>
       <c r="O5" s="3"/>
       <c r="P5" s="18"/>
       <c r="Q5" s="18"/>
@@ -1289,7 +1348,7 @@
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" s="19">
         <f t="shared" ref="C6:H6" si="0">+SUM(C3:C5)</f>
@@ -1327,9 +1386,18 @@
         <f>+SUM(K3:K5)</f>
         <v>912</v>
       </c>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
+      <c r="L6" s="19">
+        <f t="shared" ref="L6:N6" si="1">+SUM(L3:L5)</f>
+        <v>907</v>
+      </c>
+      <c r="M6" s="19">
+        <f t="shared" si="1"/>
+        <v>908</v>
+      </c>
+      <c r="N6" s="19">
+        <f t="shared" si="1"/>
+        <v>884</v>
+      </c>
       <c r="O6" s="20"/>
       <c r="P6" s="19"/>
       <c r="Q6" s="19"/>
@@ -1378,7 +1446,7 @@
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" s="4">
         <f>82+49+501</f>
@@ -1411,13 +1479,19 @@
       <c r="K8" s="4">
         <v>459</v>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
+      <c r="L8" s="4">
+        <v>491</v>
+      </c>
+      <c r="M8" s="4">
+        <v>646</v>
+      </c>
+      <c r="N8" s="4">
+        <v>433</v>
+      </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="4">
         <f>116+81+175</f>
@@ -1450,13 +1524,19 @@
       <c r="K9" s="4">
         <v>229</v>
       </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
+      <c r="L9" s="4">
+        <v>261</v>
+      </c>
+      <c r="M9" s="4">
+        <v>268</v>
+      </c>
+      <c r="N9" s="4">
+        <v>246</v>
+      </c>
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="4">
         <f>61+53+111</f>
@@ -1489,13 +1569,19 @@
       <c r="K10" s="24">
         <v>110</v>
       </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
+      <c r="L10" s="4">
+        <v>104</v>
+      </c>
+      <c r="M10" s="4">
+        <v>111</v>
+      </c>
+      <c r="N10" s="4">
+        <v>117</v>
+      </c>
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="4">
         <v>259</v>
@@ -1524,13 +1610,19 @@
       <c r="K11" s="4">
         <v>0</v>
       </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
+      <c r="L11" s="4">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" s="4">
         <v>183</v>
@@ -1559,13 +1651,19 @@
       <c r="K12" s="4">
         <v>162</v>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
+      <c r="L12" s="4">
+        <v>131</v>
+      </c>
+      <c r="M12" s="4">
+        <v>167</v>
+      </c>
+      <c r="N12" s="4">
+        <v>140</v>
+      </c>
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="3">
         <v>787</v>
@@ -1594,9 +1692,15 @@
       <c r="K13" s="3">
         <v>635</v>
       </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
+      <c r="L13" s="3">
+        <v>725</v>
+      </c>
+      <c r="M13" s="3">
+        <v>858</v>
+      </c>
+      <c r="N13" s="3">
+        <v>656</v>
+      </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
@@ -1670,9 +1774,15 @@
       <c r="K14" s="20">
         <v>797</v>
       </c>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
+      <c r="L14" s="20">
+        <v>856</v>
+      </c>
+      <c r="M14" s="20">
+        <v>1025</v>
+      </c>
+      <c r="N14" s="20">
+        <v>796</v>
+      </c>
       <c r="O14" s="20"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -1746,9 +1856,15 @@
       <c r="K15" s="3">
         <v>295</v>
       </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
+      <c r="L15" s="3">
+        <v>334</v>
+      </c>
+      <c r="M15" s="3">
+        <v>402</v>
+      </c>
+      <c r="N15" s="3">
+        <v>280</v>
+      </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
@@ -1796,27 +1912,27 @@
         <v>30</v>
       </c>
       <c r="C16" s="3">
-        <f t="shared" ref="C16:H16" si="1">+C14-C15</f>
+        <f t="shared" ref="C16:H16" si="2">+C14-C15</f>
         <v>812</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>832</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>928</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>767</v>
       </c>
       <c r="G16" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>689</v>
       </c>
       <c r="H16" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>694</v>
       </c>
       <c r="I16" s="3">
@@ -1824,16 +1940,25 @@
         <v>812</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" ref="J16:K16" si="2">+J14-J15</f>
+        <f t="shared" ref="J16:N16" si="3">+J14-J15</f>
         <v>631</v>
       </c>
       <c r="K16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>502</v>
       </c>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
+      <c r="L16" s="3">
+        <f t="shared" si="3"/>
+        <v>522</v>
+      </c>
+      <c r="M16" s="3">
+        <f t="shared" si="3"/>
+        <v>623</v>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="3"/>
+        <v>516</v>
+      </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -1907,9 +2032,15 @@
       <c r="K17" s="3">
         <v>455</v>
       </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
+      <c r="L17" s="3">
+        <v>534</v>
+      </c>
+      <c r="M17" s="3">
+        <v>577</v>
+      </c>
+      <c r="N17" s="3">
+        <v>543</v>
+      </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
@@ -1954,7 +2085,7 @@
     </row>
     <row r="18" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3">
         <v>0</v>
@@ -1983,9 +2114,15 @@
       <c r="K18" s="3">
         <v>30</v>
       </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
@@ -2059,9 +2196,15 @@
       <c r="K19" s="3">
         <v>0</v>
       </c>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0</v>
+      </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
@@ -2135,9 +2278,15 @@
       <c r="K20" s="3">
         <v>1</v>
       </c>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
@@ -2185,27 +2334,27 @@
         <v>34</v>
       </c>
       <c r="C21" s="3">
-        <f t="shared" ref="C21:H21" si="3">+C16-SUM(C17:C20)</f>
+        <f t="shared" ref="C21:H21" si="4">+C16-SUM(C17:C20)</f>
         <v>80</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>122</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-543</v>
       </c>
       <c r="G21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-38</v>
       </c>
       <c r="I21" s="3">
@@ -2213,16 +2362,25 @@
         <v>-590</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" ref="J21:K21" si="4">+J16-SUM(J17:J20)</f>
+        <f t="shared" ref="J21:N21" si="5">+J16-SUM(J17:J20)</f>
         <v>-116</v>
       </c>
       <c r="K21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
+      <c r="L21" s="3">
+        <f t="shared" si="5"/>
+        <v>-12</v>
+      </c>
+      <c r="M21" s="3">
+        <f t="shared" si="5"/>
+        <v>46</v>
+      </c>
+      <c r="N21" s="3">
+        <f t="shared" si="5"/>
+        <v>-27</v>
+      </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
@@ -2296,9 +2454,15 @@
       <c r="K22" s="3">
         <v>-18</v>
       </c>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
+      <c r="L22" s="3">
+        <v>-17</v>
+      </c>
+      <c r="M22" s="3">
+        <v>-9</v>
+      </c>
+      <c r="N22" s="3">
+        <v>-33</v>
+      </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
@@ -2343,7 +2507,7 @@
     </row>
     <row r="23" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C23" s="3">
         <v>22</v>
@@ -2375,9 +2539,15 @@
         <f>-5-1</f>
         <v>-6</v>
       </c>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
+      <c r="L23" s="3">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-4</v>
+      </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
@@ -2425,27 +2595,27 @@
         <v>36</v>
       </c>
       <c r="C24" s="3">
-        <f t="shared" ref="C24:H24" si="5">+C21-SUM(C22:C23)</f>
+        <f t="shared" ref="C24:H24" si="6">+C21-SUM(C22:C23)</f>
         <v>50</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>101</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>123</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-557</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-9</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-11</v>
       </c>
       <c r="I24" s="3">
@@ -2453,16 +2623,25 @@
         <v>-605</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" ref="J24:K24" si="6">+J21-SUM(J22:J23)</f>
+        <f t="shared" ref="J24:N24" si="7">+J21-SUM(J22:J23)</f>
         <v>-102</v>
       </c>
       <c r="K24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
+      <c r="L24" s="3">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="M24" s="3">
+        <f t="shared" si="7"/>
+        <v>55</v>
+      </c>
+      <c r="N24" s="3">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
@@ -2536,9 +2715,15 @@
       <c r="K25" s="3">
         <v>-16</v>
       </c>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
+      <c r="L25" s="3">
+        <v>36</v>
+      </c>
+      <c r="M25" s="3">
+        <v>-2</v>
+      </c>
+      <c r="N25" s="3">
+        <v>9</v>
+      </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
@@ -2586,27 +2771,27 @@
         <v>38</v>
       </c>
       <c r="C26" s="3">
-        <f t="shared" ref="C26:H26" si="7">+C24-C25</f>
+        <f t="shared" ref="C26:H26" si="8">+C24-C25</f>
         <v>48</v>
       </c>
       <c r="D26" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>105</v>
       </c>
       <c r="F26" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-472</v>
       </c>
       <c r="G26" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-12</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
       <c r="I26" s="3">
@@ -2614,16 +2799,25 @@
         <v>-546</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" ref="J26:K26" si="8">+J24-J25</f>
+        <f t="shared" ref="J26:N26" si="9">+J24-J25</f>
         <v>-644</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>56</v>
       </c>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
+      <c r="L26" s="3">
+        <f t="shared" si="9"/>
+        <v>-34</v>
+      </c>
+      <c r="M26" s="3">
+        <f t="shared" si="9"/>
+        <v>57</v>
+      </c>
+      <c r="N26" s="3">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
@@ -2667,8 +2861,8 @@
       <c r="BC26" s="3"/>
     </row>
     <row r="27" spans="2:55" x14ac:dyDescent="0.2">
-      <c r="B27" s="2" t="s">
-        <v>39</v>
+      <c r="B27" s="25" t="s">
+        <v>76</v>
       </c>
       <c r="C27" s="3">
         <v>0</v>
@@ -2697,9 +2891,15 @@
       <c r="K27" s="3">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
+      <c r="L27" s="3">
+        <v>-6</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-59</v>
+      </c>
+      <c r="N27" s="3">
+        <v>5</v>
+      </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
@@ -2744,30 +2944,30 @@
     </row>
     <row r="28" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C28" s="3">
-        <f t="shared" ref="C28:H28" si="9">+C26-C27</f>
+        <f t="shared" ref="C28:H28" si="10">+C26-C27</f>
         <v>48</v>
       </c>
       <c r="D28" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>90</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>105</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-472</v>
       </c>
       <c r="G28" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-14</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>24</v>
       </c>
       <c r="I28" s="3">
@@ -2775,16 +2975,25 @@
         <v>-547</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" ref="J28:K28" si="10">+J26-J27</f>
+        <f t="shared" ref="J28:N28" si="11">+J26-J27</f>
         <v>-645</v>
       </c>
       <c r="K28" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>53</v>
       </c>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
+      <c r="L28" s="3">
+        <f t="shared" si="11"/>
+        <v>-28</v>
+      </c>
+      <c r="M28" s="3">
+        <f t="shared" si="11"/>
+        <v>116</v>
+      </c>
+      <c r="N28" s="3">
+        <f t="shared" si="11"/>
+        <v>-4</v>
+      </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
@@ -2884,30 +3093,30 @@
     </row>
     <row r="30" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30" s="21">
-        <f t="shared" ref="C30:H30" si="11">+C28/C31</f>
+        <f t="shared" ref="C30:H30" si="12">+C28/C31</f>
         <v>0.40874739522529058</v>
       </c>
       <c r="D30" s="21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.77137988633803078</v>
       </c>
       <c r="E30" s="21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.89900814742829471</v>
       </c>
       <c r="F30" s="21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4.0288050341489452</v>
       </c>
       <c r="G30" s="21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-7.889978443564466E-2</v>
       </c>
       <c r="H30" s="21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.20258742635060734</v>
       </c>
       <c r="I30" s="21">
@@ -2915,16 +3124,25 @@
         <v>-4.6143303080704063</v>
       </c>
       <c r="J30" s="21">
-        <f t="shared" ref="J30:K30" si="12">+J28/J31</f>
+        <f t="shared" ref="J30:N30" si="13">+J28/J31</f>
         <v>-5.4396435911784842</v>
       </c>
       <c r="K30" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.28072060810609145</v>
       </c>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+      <c r="L30" s="21">
+        <f t="shared" si="13"/>
+        <v>-0.23374857013703904</v>
+      </c>
+      <c r="M30" s="21">
+        <f t="shared" si="13"/>
+        <v>0.96785812421402728</v>
+      </c>
+      <c r="N30" s="21">
+        <f t="shared" si="13"/>
+        <v>-3.36705384446883E-2</v>
+      </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
@@ -2998,9 +3216,15 @@
       <c r="K31" s="3">
         <v>188.79981900000001</v>
       </c>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
+      <c r="L31" s="3">
+        <v>119.786829</v>
+      </c>
+      <c r="M31" s="3">
+        <v>119.852277</v>
+      </c>
+      <c r="N31" s="3">
+        <v>118.798219</v>
+      </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
@@ -3100,22 +3324,22 @@
     </row>
     <row r="33" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="22">
-        <f t="shared" ref="G33:I33" si="13">+G6/C6-1</f>
+        <f t="shared" ref="G33:I33" si="14">+G6/C6-1</f>
         <v>-3.2258064516129004E-2</v>
       </c>
       <c r="H33" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-4.0977147360126032E-2</v>
       </c>
       <c r="I33" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-5.1181102362204745E-2</v>
       </c>
       <c r="J33" s="22">
@@ -3126,9 +3350,18 @@
         <f>+K6/G6-1</f>
         <v>-0.25853658536585367</v>
       </c>
-      <c r="L33" s="22"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="22"/>
+      <c r="L33" s="22">
+        <f t="shared" ref="L33:N33" si="15">+L6/H6-1</f>
+        <v>-0.25472473294987674</v>
+      </c>
+      <c r="M33" s="22">
+        <f t="shared" si="15"/>
+        <v>-0.24647302904564317</v>
+      </c>
+      <c r="N33" s="22">
+        <f t="shared" si="15"/>
+        <v>-0.23661485319516407</v>
+      </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
@@ -3173,18 +3406,18 @@
     </row>
     <row r="34" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="22">
-        <f t="shared" ref="G34:H40" si="14">+G8/C8-1</f>
+        <f t="shared" ref="G34:H40" si="16">+G8/C8-1</f>
         <v>-9.3354430379746889E-2</v>
       </c>
       <c r="H34" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.14347826086956517</v>
       </c>
       <c r="I34" s="22">
@@ -3199,9 +3432,18 @@
         <f>+K8/G8-1</f>
         <v>-0.19895287958115182</v>
       </c>
-      <c r="L34" s="22"/>
-      <c r="M34" s="22"/>
-      <c r="N34" s="22"/>
+      <c r="L34" s="22">
+        <f t="shared" ref="L34:N40" si="17">+L8/H8-1</f>
+        <v>-0.16920473773265654</v>
+      </c>
+      <c r="M34" s="22">
+        <f t="shared" si="17"/>
+        <v>-0.14323607427055707</v>
+      </c>
+      <c r="N34" s="22">
+        <f t="shared" si="17"/>
+        <v>-0.22816399286987521</v>
+      </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
@@ -3246,35 +3488,44 @@
     </row>
     <row r="35" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.18010752688172038</v>
       </c>
       <c r="H35" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.13216957605985036</v>
       </c>
       <c r="I35" s="22">
-        <f t="shared" ref="I35:K40" si="15">+I9/E9-1</f>
+        <f t="shared" ref="I35:K40" si="18">+I9/E9-1</f>
         <v>-9.3085106382978733E-2</v>
       </c>
       <c r="J35" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.14204545454545459</v>
       </c>
       <c r="K35" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.24918032786885247</v>
       </c>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="22"/>
+      <c r="L35" s="22">
+        <f t="shared" si="17"/>
+        <v>-0.25</v>
+      </c>
+      <c r="M35" s="22">
+        <f t="shared" si="17"/>
+        <v>-0.21407624633431088</v>
+      </c>
+      <c r="N35" s="22">
+        <f t="shared" si="17"/>
+        <v>-0.18543046357615889</v>
+      </c>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
@@ -3319,35 +3570,44 @@
     </row>
     <row r="36" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.16000000000000003</v>
       </c>
       <c r="H36" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.30000000000000004</v>
       </c>
       <c r="I36" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.20192307692307687</v>
       </c>
       <c r="J36" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.2321428571428571</v>
       </c>
       <c r="K36" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.41798941798941802</v>
       </c>
-      <c r="L36" s="22"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="22"/>
+      <c r="L36" s="22">
+        <f t="shared" si="17"/>
+        <v>-0.25714285714285712</v>
+      </c>
+      <c r="M36" s="22">
+        <f t="shared" si="17"/>
+        <v>-0.33132530120481929</v>
+      </c>
+      <c r="N36" s="22">
+        <f t="shared" si="17"/>
+        <v>-0.31976744186046513</v>
+      </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
@@ -3392,35 +3652,44 @@
     </row>
     <row r="37" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.15444015444015446</v>
       </c>
       <c r="H37" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.28214285714285714</v>
       </c>
       <c r="I37" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.14977973568281944</v>
       </c>
       <c r="J37" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.21212121212121215</v>
       </c>
       <c r="K37" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-1</v>
       </c>
-      <c r="L37" s="22"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22"/>
+      <c r="L37" s="22">
+        <f t="shared" si="17"/>
+        <v>-1</v>
+      </c>
+      <c r="M37" s="22">
+        <f t="shared" si="17"/>
+        <v>-1</v>
+      </c>
+      <c r="N37" s="22">
+        <f t="shared" si="17"/>
+        <v>-1</v>
+      </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
@@ -3465,35 +3734,44 @@
     </row>
     <row r="38" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-5.4644808743169349E-2</v>
       </c>
       <c r="H38" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>6.0606060606060552E-2</v>
       </c>
       <c r="I38" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-4.216867469879515E-2</v>
       </c>
       <c r="J38" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-2.9197080291970767E-2</v>
       </c>
       <c r="K38" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-6.3583815028901758E-2</v>
       </c>
-      <c r="L38" s="22"/>
-      <c r="M38" s="22"/>
-      <c r="N38" s="22"/>
+      <c r="L38" s="22">
+        <f t="shared" si="17"/>
+        <v>-6.4285714285714279E-2</v>
+      </c>
+      <c r="M38" s="22">
+        <f t="shared" si="17"/>
+        <v>5.031446540880502E-2</v>
+      </c>
+      <c r="N38" s="22">
+        <f t="shared" si="17"/>
+        <v>5.2631578947368363E-2</v>
+      </c>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
@@ -3538,35 +3816,44 @@
     </row>
     <row r="39" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.14231257941550191</v>
       </c>
       <c r="H39" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.16040955631399323</v>
       </c>
       <c r="I39" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.120889748549323</v>
       </c>
       <c r="J39" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.15571776155717765</v>
       </c>
       <c r="K39" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-5.9259259259259234E-2</v>
       </c>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="22"/>
+      <c r="L39" s="22">
+        <f t="shared" si="17"/>
+        <v>-1.7615176151761558E-2</v>
+      </c>
+      <c r="M39" s="22">
+        <f t="shared" si="17"/>
+        <v>-5.6105610561056118E-2</v>
+      </c>
+      <c r="N39" s="22">
+        <f t="shared" si="17"/>
+        <v>-5.4755043227665667E-2</v>
+      </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
@@ -3611,35 +3898,44 @@
     </row>
     <row r="40" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="20"/>
       <c r="E40" s="20"/>
       <c r="F40" s="20"/>
       <c r="G40" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.13181448331977219</v>
       </c>
       <c r="H40" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.16421378776142526</v>
       </c>
       <c r="I40" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.11632796075683249</v>
       </c>
       <c r="J40" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.1537203597710548</v>
       </c>
       <c r="K40" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-0.25304592314901597</v>
       </c>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="23"/>
+      <c r="L40" s="23">
+        <f t="shared" si="17"/>
+        <v>-0.20667284522706209</v>
+      </c>
+      <c r="M40" s="23">
+        <f t="shared" si="17"/>
+        <v>-0.18715305313243458</v>
+      </c>
+      <c r="N40" s="23">
+        <f t="shared" si="17"/>
+        <v>-0.23091787439613531</v>
+      </c>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
@@ -3684,30 +3980,30 @@
     </row>
     <row r="41" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C41" s="22">
-        <f t="shared" ref="C41:H41" si="16">+C16/C14</f>
+        <f t="shared" ref="C41:H41" si="19">+C16/C14</f>
         <v>0.66069975589910501</v>
       </c>
       <c r="D41" s="22">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.64446165762974439</v>
       </c>
       <c r="E41" s="22">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.65031534688156978</v>
       </c>
       <c r="F41" s="22">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.62714636140637781</v>
       </c>
       <c r="G41" s="22">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.64573570759137766</v>
       </c>
       <c r="H41" s="22">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.64318813716404077</v>
       </c>
       <c r="I41" s="22">
@@ -3722,9 +4018,18 @@
         <f>+K16/K14</f>
         <v>0.62986198243412794</v>
       </c>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
-      <c r="N41" s="22"/>
+      <c r="L41" s="22">
+        <f t="shared" ref="L41:N41" si="20">+L16/L14</f>
+        <v>0.60981308411214952</v>
+      </c>
+      <c r="M41" s="22">
+        <f t="shared" si="20"/>
+        <v>0.60780487804878047</v>
+      </c>
+      <c r="N41" s="22">
+        <f t="shared" si="20"/>
+        <v>0.64824120603015079</v>
+      </c>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
@@ -3769,30 +4074,30 @@
     </row>
     <row r="42" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C42" s="22">
-        <f t="shared" ref="C42:H42" si="17">+C21/C14</f>
+        <f t="shared" ref="C42:H42" si="21">+C21/C14</f>
         <v>6.5093572009764039E-2</v>
       </c>
       <c r="D42" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>7.745933384972889E-2</v>
       </c>
       <c r="E42" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>8.5494043447792573E-2</v>
       </c>
       <c r="F42" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-0.4439901880621423</v>
       </c>
       <c r="G42" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-7.4976569821930648E-3</v>
       </c>
       <c r="H42" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-3.5217794253938832E-2</v>
       </c>
       <c r="I42" s="22">
@@ -3807,9 +4112,18 @@
         <f>+K21/K14</f>
         <v>2.0075282308657464E-2</v>
       </c>
-      <c r="L42" s="22"/>
-      <c r="M42" s="22"/>
-      <c r="N42" s="22"/>
+      <c r="L42" s="22">
+        <f t="shared" ref="L42:N42" si="22">+L21/L14</f>
+        <v>-1.4018691588785047E-2</v>
+      </c>
+      <c r="M42" s="22">
+        <f t="shared" si="22"/>
+        <v>4.4878048780487803E-2</v>
+      </c>
+      <c r="N42" s="22">
+        <f t="shared" si="22"/>
+        <v>-3.391959798994975E-2</v>
+      </c>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
@@ -3854,30 +4168,30 @@
     </row>
     <row r="43" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C43" s="22">
-        <f t="shared" ref="C43:H43" si="18">+C25/C24</f>
+        <f t="shared" ref="C43:H43" si="23">+C25/C24</f>
         <v>0.04</v>
       </c>
       <c r="D43" s="22">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0.10891089108910891</v>
       </c>
       <c r="E43" s="22">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0.14634146341463414</v>
       </c>
       <c r="F43" s="22">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0.15260323159784561</v>
       </c>
       <c r="G43" s="22">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>-0.33333333333333331</v>
       </c>
       <c r="H43" s="22">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>3.0909090909090908</v>
       </c>
       <c r="I43" s="22">
@@ -3892,9 +4206,18 @@
         <f>+K25/K24</f>
         <v>-0.4</v>
       </c>
-      <c r="L43" s="22"/>
-      <c r="M43" s="22"/>
-      <c r="N43" s="22"/>
+      <c r="L43" s="22">
+        <f t="shared" ref="L43:N43" si="24">+L25/L24</f>
+        <v>18</v>
+      </c>
+      <c r="M43" s="22">
+        <f t="shared" si="24"/>
+        <v>-3.6363636363636362E-2</v>
+      </c>
+      <c r="N43" s="22">
+        <f t="shared" si="24"/>
+        <v>0.9</v>
+      </c>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
